--- a/pythonProject15/rooms.xlsx
+++ b/pythonProject15/rooms.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="11471" windowHeight="8735"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
   <si>
     <t>教室编号</t>
   </si>
@@ -50,16 +50,10 @@
     <t>可用时间</t>
   </si>
   <si>
-    <t>R2025000</t>
-  </si>
-  <si>
-    <t>计算机实验室A</t>
-  </si>
-  <si>
-    <t>工程楼</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>计算机基础</t>
+  </si>
+  <si>
+    <t>实训楼</t>
   </si>
   <si>
     <t>1,2,3,4,5</t>
@@ -68,82 +62,25 @@
     <t>08:00-22:00</t>
   </si>
   <si>
-    <t>R2025001</t>
-  </si>
-  <si>
-    <t>多媒体教室B</t>
-  </si>
-  <si>
-    <t>教学主楼</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>R2025002</t>
-  </si>
-  <si>
-    <t>语言实验室C</t>
-  </si>
-  <si>
-    <t>实验楼</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>R2025003</t>
-  </si>
-  <si>
-    <t>物理实验室D</t>
-  </si>
-  <si>
-    <t>科技楼</t>
-  </si>
-  <si>
-    <t>R2025004</t>
-  </si>
-  <si>
-    <t>化学实验室E</t>
-  </si>
-  <si>
-    <t>综合楼</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>R2025005</t>
-  </si>
-  <si>
-    <t>计算机实验室F</t>
-  </si>
-  <si>
-    <t>R2025006</t>
-  </si>
-  <si>
-    <t>电子实验室G</t>
-  </si>
-  <si>
-    <t>R2025007</t>
-  </si>
-  <si>
-    <t>生物实验室H</t>
-  </si>
-  <si>
-    <t>R2025008</t>
-  </si>
-  <si>
-    <t>地理信息实验室I</t>
-  </si>
-  <si>
-    <t>R2025009</t>
-  </si>
-  <si>
-    <t>机械制图室J</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>云计算实验室</t>
+  </si>
+  <si>
+    <t>安全仿真对抗</t>
+  </si>
+  <si>
+    <t>信息安全基础</t>
+  </si>
+  <si>
+    <t>3D打印</t>
+  </si>
+  <si>
+    <t>存储设备操作</t>
+  </si>
+  <si>
+    <t>单片机实验室</t>
+  </si>
+  <si>
+    <t>ARM A9实验室</t>
   </si>
 </sst>
 </file>
@@ -156,7 +93,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,13 +104,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -640,157 +570,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -843,7 +778,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -853,9 +1002,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -863,39 +1012,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -927,6 +1076,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -961,171 +1111,135 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1136,9 +1250,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="2" width="14.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="13.6666666666667" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -1163,235 +1282,207 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>406</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>408</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>413</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
+      <c r="C4">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2"/>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>415</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>431</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C3">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>441</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C7">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>443</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
+      <c r="C8">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2"/>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>449</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
+      <c r="C9">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
+    <row r="10" spans="6:8">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
+    <row r="11" spans="6:8">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
